--- a/output/Tables/7000 steps/HIA_age_7000steps_1000replicate.xlsx
+++ b/output/Tables/7000 steps/HIA_age_7000steps_1000replicate.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>1089.681</v>
+        <v>1067.276</v>
       </c>
       <c r="D2">
-        <v>1010.523</v>
+        <v>989.949</v>
       </c>
       <c r="E2">
-        <v>1168.891</v>
+        <v>1144.88</v>
       </c>
       <c r="F2">
-        <v>62167.64</v>
+        <v>60895.056</v>
       </c>
       <c r="G2">
-        <v>57713.077</v>
+        <v>56517.32</v>
       </c>
       <c r="H2">
-        <v>66644.227</v>
+        <v>65247.439</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>8268457035.931</v>
+        <v>8096973642.799</v>
       </c>
       <c r="M2">
-        <v>7673525254.104</v>
+        <v>7516198852.163</v>
       </c>
       <c r="N2">
-        <v>8861519251.393</v>
+        <v>8680404113.207001</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>2384.956</v>
+        <v>2314.607</v>
       </c>
       <c r="D3">
-        <v>2232.76</v>
+        <v>2167.914</v>
       </c>
       <c r="E3">
-        <v>2535.936</v>
+        <v>2460.522</v>
       </c>
       <c r="F3">
-        <v>109950.056</v>
+        <v>106705.248</v>
       </c>
       <c r="G3">
-        <v>103258.943</v>
+        <v>100229.315</v>
       </c>
       <c r="H3">
-        <v>116629.578</v>
+        <v>113205.401</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>14622036742.042</v>
+        <v>14192100380.338</v>
       </c>
       <c r="M3">
-        <v>13730466751.466</v>
+        <v>13329420730.252</v>
       </c>
       <c r="N3">
-        <v>15520374973.852</v>
+        <v>15066846787.853</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>7067.38</v>
+        <v>6866.934</v>
       </c>
       <c r="D4">
-        <v>6648.928</v>
+        <v>6461.127</v>
       </c>
       <c r="E4">
-        <v>7482.965</v>
+        <v>7274.025</v>
       </c>
       <c r="F4">
-        <v>258534.63</v>
+        <v>251250.301</v>
       </c>
       <c r="G4">
-        <v>243814.762</v>
+        <v>236948.11</v>
       </c>
       <c r="H4">
-        <v>273229.975</v>
+        <v>265579.543</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>34391483282.894</v>
+        <v>33423596566.512</v>
       </c>
       <c r="M4">
-        <v>32429227877.172</v>
+        <v>31509885542.863</v>
       </c>
       <c r="N4">
-        <v>36362772132.709</v>
+        <v>35318092226.768</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>14322.771</v>
+        <v>14102.617</v>
       </c>
       <c r="D5">
-        <v>13598.578</v>
+        <v>13399.691</v>
       </c>
       <c r="E5">
-        <v>15049.08</v>
+        <v>14812.494</v>
       </c>
       <c r="F5">
-        <v>382159.404</v>
+        <v>376542.016</v>
       </c>
       <c r="G5">
-        <v>363781.033</v>
+        <v>358644.037</v>
       </c>
       <c r="H5">
-        <v>400524.785</v>
+        <v>394384.184</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>50830160284.168</v>
+        <v>50082534917.479</v>
       </c>
       <c r="M5">
-        <v>48375753179.612</v>
+        <v>47704446490.197</v>
       </c>
       <c r="N5">
-        <v>53281950089.533</v>
+        <v>52464750971.198</v>
       </c>
     </row>
     <row r="6">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>28291.527</v>
+        <v>27953.075</v>
       </c>
       <c r="D6">
-        <v>26934.315</v>
+        <v>26635.107</v>
       </c>
       <c r="E6">
-        <v>29651.409</v>
+        <v>29284.68</v>
       </c>
       <c r="F6">
-        <v>478394.419</v>
+        <v>472689.265</v>
       </c>
       <c r="G6">
-        <v>456471.074</v>
+        <v>451260.186</v>
       </c>
       <c r="H6">
-        <v>500416.54</v>
+        <v>494060.845</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>63626676278.552</v>
+        <v>62864477733.612</v>
       </c>
       <c r="M6">
-        <v>60706807783.388</v>
+        <v>60018882631.298</v>
       </c>
       <c r="N6">
-        <v>66549148389.503</v>
+        <v>65702559584.357</v>
       </c>
     </row>
     <row r="7">
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>42654.439</v>
+        <v>43170.822</v>
       </c>
       <c r="D7">
-        <v>40236.532</v>
+        <v>40779.551</v>
       </c>
       <c r="E7">
-        <v>45071.676</v>
+        <v>45551.606</v>
       </c>
       <c r="F7">
-        <v>310700.772</v>
+        <v>314717.319</v>
       </c>
       <c r="G7">
-        <v>295127.35</v>
+        <v>299334.688</v>
       </c>
       <c r="H7">
-        <v>326242.767</v>
+        <v>330020.785</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>41316229515.424</v>
+        <v>41856649745.888</v>
       </c>
       <c r="M7">
-        <v>39255338899.644</v>
+        <v>39815667875.427</v>
       </c>
       <c r="N7">
-        <v>43375802739.703</v>
+        <v>43901437594.068</v>
       </c>
     </row>
     <row r="8">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>63115.473</v>
+        <v>71701.486</v>
       </c>
       <c r="D8">
-        <v>58094.457</v>
+        <v>66458.234</v>
       </c>
       <c r="E8">
-        <v>68127.951</v>
+        <v>76948.56</v>
       </c>
       <c r="F8">
-        <v>50151.063</v>
+        <v>55542.495</v>
       </c>
       <c r="G8">
-        <v>44528.198</v>
+        <v>49746.478</v>
       </c>
       <c r="H8">
-        <v>55790.699</v>
+        <v>61319.209</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>6669183892.697</v>
+        <v>7388261803.205</v>
       </c>
       <c r="M8">
-        <v>5922790174.294</v>
+        <v>6623354927.168</v>
       </c>
       <c r="N8">
-        <v>7417852854.851</v>
+        <v>8157590086.41</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>763.558</v>
+        <v>668.174</v>
       </c>
       <c r="D9">
-        <v>707.972</v>
+        <v>619.422</v>
       </c>
       <c r="E9">
-        <v>819.6369999999999</v>
+        <v>717.391</v>
       </c>
       <c r="F9">
-        <v>2892.342</v>
+        <v>1439.558</v>
       </c>
       <c r="G9">
-        <v>2680.944</v>
+        <v>1340.073</v>
       </c>
       <c r="H9">
-        <v>3106.485</v>
+        <v>1540.337</v>
       </c>
       <c r="I9">
-        <v>42522252.144</v>
+        <v>35206635.403</v>
       </c>
       <c r="J9">
-        <v>39433534.431</v>
+        <v>32635233.341</v>
       </c>
       <c r="K9">
-        <v>45631955.659</v>
+        <v>37813686.655</v>
       </c>
       <c r="L9">
-        <v>384638580.13</v>
+        <v>191497836.908</v>
       </c>
       <c r="M9">
-        <v>356508479.633</v>
+        <v>178267045.061</v>
       </c>
       <c r="N9">
-        <v>413222812.784</v>
+        <v>204888701.68</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>1805.05</v>
+        <v>1559.835</v>
       </c>
       <c r="D10">
-        <v>1693.908</v>
+        <v>1463.804</v>
       </c>
       <c r="E10">
-        <v>1916.139</v>
+        <v>1656.848</v>
       </c>
       <c r="F10">
-        <v>5561.592</v>
+        <v>3836.848</v>
       </c>
       <c r="G10">
-        <v>5224.788</v>
+        <v>3608.8</v>
       </c>
       <c r="H10">
-        <v>5902.214</v>
+        <v>4066.344</v>
       </c>
       <c r="I10">
-        <v>100528859.155</v>
+        <v>82195947.61300001</v>
       </c>
       <c r="J10">
-        <v>94378734.853</v>
+        <v>77140342.55599999</v>
       </c>
       <c r="K10">
-        <v>106764101.495</v>
+        <v>87292014.17200001</v>
       </c>
       <c r="L10">
-        <v>739662725.785</v>
+        <v>510260006.638</v>
       </c>
       <c r="M10">
-        <v>694755769.409</v>
+        <v>480003690.966</v>
       </c>
       <c r="N10">
-        <v>785146768.674</v>
+        <v>540821296.039</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>6890.468</v>
+        <v>6039.915</v>
       </c>
       <c r="D11">
-        <v>6475.195</v>
+        <v>5672.544</v>
       </c>
       <c r="E11">
-        <v>7308.086</v>
+        <v>6407.638</v>
       </c>
       <c r="F11">
-        <v>16958.899</v>
+        <v>13341.113</v>
       </c>
       <c r="G11">
-        <v>15930.318</v>
+        <v>12559.497</v>
       </c>
       <c r="H11">
-        <v>17987.007</v>
+        <v>14141.395</v>
       </c>
       <c r="I11">
-        <v>383779268.014</v>
+        <v>318263921.02</v>
       </c>
       <c r="J11">
-        <v>360779321.581</v>
+        <v>299036607.131</v>
       </c>
       <c r="K11">
-        <v>407163523.322</v>
+        <v>337671560.775</v>
       </c>
       <c r="L11">
-        <v>2255445251.988</v>
+        <v>1774253119.617</v>
       </c>
       <c r="M11">
-        <v>2119206585.63</v>
+        <v>1670251203.154</v>
       </c>
       <c r="N11">
-        <v>2392123627.096</v>
+        <v>1880297151.794</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>15335.848</v>
+        <v>13544.235</v>
       </c>
       <c r="D12">
-        <v>14561.809</v>
+        <v>12861.499</v>
       </c>
       <c r="E12">
-        <v>16114.963</v>
+        <v>14232.664</v>
       </c>
       <c r="F12">
-        <v>27521.334</v>
+        <v>25554.546</v>
       </c>
       <c r="G12">
-        <v>26149.689</v>
+        <v>24303.472</v>
       </c>
       <c r="H12">
-        <v>28914.97</v>
+        <v>26818.258</v>
       </c>
       <c r="I12">
-        <v>854297678.391</v>
+        <v>713677590.393</v>
       </c>
       <c r="J12">
-        <v>810884247.89</v>
+        <v>677802054.043</v>
       </c>
       <c r="K12">
-        <v>897596518.6720001</v>
+        <v>750008739.641</v>
       </c>
       <c r="L12">
-        <v>3659991611.155</v>
+        <v>3398674774.659</v>
       </c>
       <c r="M12">
-        <v>3477828497.775</v>
+        <v>3231816707.566</v>
       </c>
       <c r="N12">
-        <v>3845295311.175</v>
+        <v>3567238721.961</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>41290.246</v>
+        <v>36437.142</v>
       </c>
       <c r="D13">
-        <v>39300.321</v>
+        <v>34698.563</v>
       </c>
       <c r="E13">
-        <v>43277.956</v>
+        <v>38187.388</v>
       </c>
       <c r="F13">
-        <v>48539.728</v>
+        <v>50694.123</v>
       </c>
       <c r="G13">
-        <v>46179.685</v>
+        <v>48302.649</v>
       </c>
       <c r="H13">
-        <v>50916.821</v>
+        <v>53104.29</v>
       </c>
       <c r="I13">
-        <v>2300182584.386</v>
+        <v>1919955970.202</v>
       </c>
       <c r="J13">
-        <v>2189819743.318</v>
+        <v>1828008894.246</v>
       </c>
       <c r="K13">
-        <v>2411211199.576</v>
+        <v>2012218505.601</v>
       </c>
       <c r="L13">
-        <v>6455627367.512</v>
+        <v>6742514271.019</v>
       </c>
       <c r="M13">
-        <v>6141960436.63</v>
+        <v>6423920462.036</v>
       </c>
       <c r="N13">
-        <v>6771460756.993</v>
+        <v>7063702164.181</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>45928.541</v>
+        <v>41517.697</v>
       </c>
       <c r="D14">
-        <v>43536.102</v>
+        <v>39397.414</v>
       </c>
       <c r="E14">
-        <v>48327.27</v>
+        <v>43652.229</v>
       </c>
       <c r="F14">
-        <v>26367.06</v>
+        <v>51187.774</v>
       </c>
       <c r="G14">
-        <v>24939.092</v>
+        <v>48539.928</v>
       </c>
       <c r="H14">
-        <v>27814.67</v>
+        <v>53857.782</v>
       </c>
       <c r="I14">
-        <v>2558540639.087</v>
+        <v>2187709207.081</v>
       </c>
       <c r="J14">
-        <v>2425285027.253</v>
+        <v>2076594476.559</v>
       </c>
       <c r="K14">
-        <v>2691690774.447</v>
+        <v>2300253309.044</v>
       </c>
       <c r="L14">
-        <v>3506636825.198</v>
+        <v>6808829153.028</v>
       </c>
       <c r="M14">
-        <v>3316030589.139</v>
+        <v>6457866670.281</v>
       </c>
       <c r="N14">
-        <v>3698402111.104</v>
+        <v>7162611457.883</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>33850.838</v>
+        <v>33843.589</v>
       </c>
       <c r="D15">
-        <v>31309.113</v>
+        <v>31478.858</v>
       </c>
       <c r="E15">
-        <v>36409.141</v>
+        <v>36223.65</v>
       </c>
       <c r="F15">
-        <v>2818.782</v>
+        <v>35758.473</v>
       </c>
       <c r="G15">
-        <v>2470.848</v>
+        <v>33252.538</v>
       </c>
       <c r="H15">
-        <v>3172.684</v>
+        <v>38301.433</v>
       </c>
       <c r="I15">
-        <v>1885676121.504</v>
+        <v>1783008883.509</v>
       </c>
       <c r="J15">
-        <v>1744235384.975</v>
+        <v>1658501731.263</v>
       </c>
       <c r="K15">
-        <v>2028168341.544</v>
+        <v>1909118620.17</v>
       </c>
       <c r="L15">
-        <v>374840831.763</v>
+        <v>4755550346.575</v>
       </c>
       <c r="M15">
-        <v>328457947.822</v>
+        <v>4419936104.261</v>
       </c>
       <c r="N15">
-        <v>421661057.995</v>
+        <v>5094525319.133</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>7352.697</v>
+        <v>241.586</v>
       </c>
       <c r="D16">
-        <v>6668.488</v>
+        <v>223.902</v>
       </c>
       <c r="E16">
-        <v>8067.191</v>
+        <v>259.629</v>
       </c>
       <c r="F16">
-        <v>24851.183</v>
+        <v>147.392</v>
       </c>
       <c r="G16">
-        <v>22464.316</v>
+        <v>136.445</v>
       </c>
       <c r="H16">
-        <v>27363.277</v>
+        <v>158.649</v>
       </c>
       <c r="I16">
-        <v>108848026.842</v>
+        <v>7084872.67</v>
       </c>
       <c r="J16">
-        <v>98752210.441</v>
+        <v>6565172.288</v>
       </c>
       <c r="K16">
-        <v>119394344.012</v>
+        <v>7617110.58</v>
       </c>
       <c r="L16">
-        <v>3304767583.304</v>
+        <v>19604458.009</v>
       </c>
       <c r="M16">
-        <v>2990942055.291</v>
+        <v>18150765.474</v>
       </c>
       <c r="N16">
-        <v>3639848230.823</v>
+        <v>21094301.272</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>12788.501</v>
+        <v>771.01</v>
       </c>
       <c r="D17">
-        <v>11731.411</v>
+        <v>722.1900000000001</v>
       </c>
       <c r="E17">
-        <v>13880.821</v>
+        <v>820.9640000000001</v>
       </c>
       <c r="F17">
-        <v>35734.04</v>
+        <v>459.738</v>
       </c>
       <c r="G17">
-        <v>32710.28</v>
+        <v>430.267</v>
       </c>
       <c r="H17">
-        <v>38884.753</v>
+        <v>489.732</v>
       </c>
       <c r="I17">
-        <v>189366630.336</v>
+        <v>22607486.483</v>
       </c>
       <c r="J17">
-        <v>173697666.594</v>
+        <v>21170658.242</v>
       </c>
       <c r="K17">
-        <v>205642672.498</v>
+        <v>24054620.326</v>
       </c>
       <c r="L17">
-        <v>4753480551.743</v>
+        <v>61140539.646</v>
       </c>
       <c r="M17">
-        <v>4350951181.105</v>
+        <v>57226156.157</v>
       </c>
       <c r="N17">
-        <v>5172607832.056</v>
+        <v>65135616.911</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>20509.025</v>
+        <v>2130.33</v>
       </c>
       <c r="D18">
-        <v>18961.283</v>
+        <v>2000.141</v>
       </c>
       <c r="E18">
-        <v>22107.236</v>
+        <v>2263.932</v>
       </c>
       <c r="F18">
-        <v>46008.567</v>
+        <v>1185.325</v>
       </c>
       <c r="G18">
-        <v>42363.117</v>
+        <v>1110.356</v>
       </c>
       <c r="H18">
-        <v>49804.151</v>
+        <v>1261.666</v>
       </c>
       <c r="I18">
-        <v>303689769.066</v>
+        <v>62473254.692</v>
       </c>
       <c r="J18">
-        <v>280664695.324</v>
+        <v>58614499.635</v>
       </c>
       <c r="K18">
-        <v>327402290.839</v>
+        <v>66374205.487</v>
       </c>
       <c r="L18">
-        <v>6118924337.99</v>
+        <v>157618300.012</v>
       </c>
       <c r="M18">
-        <v>5632035020.269</v>
+        <v>147662490.412</v>
       </c>
       <c r="N18">
-        <v>6621656436.896</v>
+        <v>167755736.298</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>25621.114</v>
+        <v>4240.795</v>
       </c>
       <c r="D19">
-        <v>24064.608</v>
+        <v>4022.16</v>
       </c>
       <c r="E19">
-        <v>27227.942</v>
+        <v>4460.268</v>
       </c>
       <c r="F19">
-        <v>41933.988</v>
+        <v>2193.393</v>
       </c>
       <c r="G19">
-        <v>39261.794</v>
+        <v>2079.579</v>
       </c>
       <c r="H19">
-        <v>44708.428</v>
+        <v>2308.411</v>
       </c>
       <c r="I19">
-        <v>379434069.707</v>
+        <v>124345541.355</v>
       </c>
       <c r="J19">
-        <v>356406598.93</v>
+        <v>117896475.994</v>
       </c>
       <c r="K19">
-        <v>403278363.437</v>
+        <v>130825460.738</v>
       </c>
       <c r="L19">
-        <v>5577328060.208</v>
+        <v>291727059.621</v>
       </c>
       <c r="M19">
-        <v>5223932716.844</v>
+        <v>276556898.23</v>
       </c>
       <c r="N19">
-        <v>5946155718.272</v>
+        <v>306999663.406</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>32382.16</v>
+        <v>8643.503000000001</v>
       </c>
       <c r="D20">
-        <v>30606.807</v>
+        <v>8200.147999999999</v>
       </c>
       <c r="E20">
-        <v>34200.551</v>
+        <v>9094.769</v>
       </c>
       <c r="F20">
-        <v>34168.184</v>
+        <v>4234.439</v>
       </c>
       <c r="G20">
-        <v>32193.915</v>
+        <v>4023.313</v>
       </c>
       <c r="H20">
-        <v>36201.136</v>
+        <v>4449.392</v>
       </c>
       <c r="I20">
-        <v>479461233.66</v>
+        <v>253397079.934</v>
       </c>
       <c r="J20">
-        <v>453132672.56</v>
+        <v>240404357.523</v>
       </c>
       <c r="K20">
-        <v>506533807.393</v>
+        <v>266629164.667</v>
       </c>
       <c r="L20">
-        <v>4544495366.256</v>
+        <v>563139323.352</v>
       </c>
       <c r="M20">
-        <v>4282831906.929</v>
+        <v>535105735.231</v>
       </c>
       <c r="N20">
-        <v>4814629557.991</v>
+        <v>591686926.1059999</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>21574.217</v>
+        <v>8302.566000000001</v>
       </c>
       <c r="D21">
-        <v>20231.77</v>
+        <v>7823.228</v>
       </c>
       <c r="E21">
-        <v>22949.178</v>
+        <v>8787.299999999999</v>
       </c>
       <c r="F21">
-        <v>10655.435</v>
+        <v>3746.004</v>
       </c>
       <c r="G21">
-        <v>9957.656000000001</v>
+        <v>3535.121</v>
       </c>
       <c r="H21">
-        <v>11372.823</v>
+        <v>3960.051</v>
       </c>
       <c r="I21">
-        <v>319457481.855</v>
+        <v>243411805.582</v>
       </c>
       <c r="J21">
-        <v>299470475.577</v>
+        <v>229440159.353</v>
       </c>
       <c r="K21">
-        <v>339803447.001</v>
+        <v>257725812.351</v>
       </c>
       <c r="L21">
-        <v>1417091211.804</v>
+        <v>498109467.343</v>
       </c>
       <c r="M21">
-        <v>1324309638.588</v>
+        <v>470120014.006</v>
       </c>
       <c r="N21">
-        <v>1512439299.512</v>
+        <v>526698143.872</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>9908.245999999999</v>
+        <v>5460.2</v>
       </c>
       <c r="D22">
-        <v>8990.181</v>
+        <v>5032.428</v>
       </c>
       <c r="E22">
-        <v>10855.247</v>
+        <v>5895.621</v>
       </c>
       <c r="F22">
-        <v>636.212</v>
+        <v>1890.025</v>
       </c>
       <c r="G22">
-        <v>543.491</v>
+        <v>1746.592</v>
       </c>
       <c r="H22">
-        <v>733.068</v>
+        <v>2036.706</v>
       </c>
       <c r="I22">
-        <v>146686360.694</v>
+        <v>160104942.116</v>
       </c>
       <c r="J22">
-        <v>133072279.127</v>
+        <v>147451703.597</v>
       </c>
       <c r="K22">
-        <v>160720969.652</v>
+        <v>172953162.166</v>
       </c>
       <c r="L22">
-        <v>84606083.479</v>
+        <v>251348362.326</v>
       </c>
       <c r="M22">
-        <v>72230635.984</v>
+        <v>232134139.158</v>
       </c>
       <c r="N22">
-        <v>97519017.271</v>
+        <v>270776730.743</v>
       </c>
     </row>
     <row r="23">
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="C23">
-        <v>1567.521</v>
+        <v>1147.196</v>
       </c>
       <c r="D23">
-        <v>1439.194</v>
+        <v>1062.327</v>
       </c>
       <c r="E23">
-        <v>1700.565</v>
+        <v>1234.101</v>
       </c>
       <c r="F23">
-        <v>6328.622</v>
+        <v>633.746</v>
       </c>
       <c r="G23">
-        <v>5801.345</v>
+        <v>586.704</v>
       </c>
       <c r="H23">
-        <v>6871.62</v>
+        <v>682.398</v>
       </c>
       <c r="I23">
-        <v>117848007.426</v>
+        <v>44975387.68</v>
       </c>
       <c r="J23">
-        <v>108227536.304</v>
+        <v>41653092.261</v>
       </c>
       <c r="K23">
-        <v>127867837.337</v>
+        <v>48382860.945</v>
       </c>
       <c r="L23">
-        <v>841717666.686</v>
+        <v>84302053.28300001</v>
       </c>
       <c r="M23">
-        <v>771895862.001</v>
+        <v>78022160.32799999</v>
       </c>
       <c r="N23">
-        <v>914543061.0930001</v>
+        <v>90733241.495</v>
       </c>
     </row>
     <row r="24">
@@ -1494,40 +1494,40 @@
         </is>
       </c>
       <c r="C24">
-        <v>2835.075</v>
+        <v>2069.413</v>
       </c>
       <c r="D24">
-        <v>2632.214</v>
+        <v>1936.426</v>
       </c>
       <c r="E24">
-        <v>3042.39</v>
+        <v>2204.267</v>
       </c>
       <c r="F24">
-        <v>9280.495000000001</v>
+        <v>1977.628</v>
       </c>
       <c r="G24">
-        <v>8620.054</v>
+        <v>1849.87</v>
       </c>
       <c r="H24">
-        <v>9958.044</v>
+        <v>2106.833</v>
       </c>
       <c r="I24">
-        <v>213234815.476</v>
+        <v>81112384.83499999</v>
       </c>
       <c r="J24">
-        <v>198073565.851</v>
+        <v>75890017.61399999</v>
       </c>
       <c r="K24">
-        <v>228737472.533</v>
+        <v>86422252.367</v>
       </c>
       <c r="L24">
-        <v>1234739358.601</v>
+        <v>262997377.822</v>
       </c>
       <c r="M24">
-        <v>1146698055.839</v>
+        <v>246051459.025</v>
       </c>
       <c r="N24">
-        <v>1324835130.263</v>
+        <v>280206342.929</v>
       </c>
     </row>
     <row r="25">
@@ -1542,40 +1542,40 @@
         </is>
       </c>
       <c r="C25">
-        <v>4850.269</v>
+        <v>3508.496</v>
       </c>
       <c r="D25">
-        <v>4503.636</v>
+        <v>3282.984</v>
       </c>
       <c r="E25">
-        <v>5206.447</v>
+        <v>3735.857</v>
       </c>
       <c r="F25">
-        <v>12612.319</v>
+        <v>4420.162</v>
       </c>
       <c r="G25">
-        <v>11708.303</v>
+        <v>4136.234</v>
       </c>
       <c r="H25">
-        <v>13542.168</v>
+        <v>4712.611</v>
       </c>
       <c r="I25">
-        <v>364730026.928</v>
+        <v>137530561.069</v>
       </c>
       <c r="J25">
-        <v>338837135.953</v>
+        <v>128741012.496</v>
       </c>
       <c r="K25">
-        <v>391525708.262</v>
+        <v>146500822.207</v>
       </c>
       <c r="L25">
-        <v>1677240151.008</v>
+        <v>588013206.6339999</v>
       </c>
       <c r="M25">
-        <v>1557072004.269</v>
+        <v>550071266.7869999</v>
       </c>
       <c r="N25">
-        <v>1801564628.428</v>
+        <v>626485450.725</v>
       </c>
     </row>
     <row r="26">
@@ -1590,40 +1590,40 @@
         </is>
       </c>
       <c r="C26">
-        <v>7113.08</v>
+        <v>5260.567</v>
       </c>
       <c r="D26">
-        <v>6703.379</v>
+        <v>4990.415</v>
       </c>
       <c r="E26">
-        <v>7532.607</v>
+        <v>5532.97</v>
       </c>
       <c r="F26">
-        <v>13696.07</v>
+        <v>6513.647</v>
       </c>
       <c r="G26">
-        <v>12902.681</v>
+        <v>6168.842</v>
       </c>
       <c r="H26">
-        <v>14505.745</v>
+        <v>6864.92</v>
       </c>
       <c r="I26">
-        <v>534898043.887</v>
+        <v>206181375.248</v>
       </c>
       <c r="J26">
-        <v>504242646.643</v>
+        <v>195649503.32</v>
       </c>
       <c r="K26">
-        <v>566498834.7079999</v>
+        <v>216898543.533</v>
       </c>
       <c r="L26">
-        <v>1821887243.811</v>
+        <v>866245098.55</v>
       </c>
       <c r="M26">
-        <v>1716959198.264</v>
+        <v>820292883.831</v>
       </c>
       <c r="N26">
-        <v>1929566195.465</v>
+        <v>912769421.766</v>
       </c>
     </row>
     <row r="27">
@@ -1638,40 +1638,40 @@
         </is>
       </c>
       <c r="C27">
-        <v>8542.942999999999</v>
+        <v>6299.242</v>
       </c>
       <c r="D27">
-        <v>8083.973</v>
+        <v>5999.716</v>
       </c>
       <c r="E27">
-        <v>9014.67</v>
+        <v>6603.596</v>
       </c>
       <c r="F27">
-        <v>10975.667</v>
+        <v>10673.639</v>
       </c>
       <c r="G27">
-        <v>10364.158</v>
+        <v>10134.136</v>
       </c>
       <c r="H27">
-        <v>11608.113</v>
+        <v>11222.133</v>
       </c>
       <c r="I27">
-        <v>642405025.7690001</v>
+        <v>246945440.635</v>
       </c>
       <c r="J27">
-        <v>607852699.727</v>
+        <v>235204778.817</v>
       </c>
       <c r="K27">
-        <v>677737484.0089999</v>
+        <v>258874162.098</v>
       </c>
       <c r="L27">
-        <v>1460387436.91</v>
+        <v>1419570343.749</v>
       </c>
       <c r="M27">
-        <v>1378764715.492</v>
+        <v>1347325394.259</v>
       </c>
       <c r="N27">
-        <v>1543401545.5</v>
+        <v>1492800671.161</v>
       </c>
     </row>
     <row r="28">
@@ -1686,40 +1686,40 @@
         </is>
       </c>
       <c r="C28">
-        <v>2734.138</v>
+        <v>2065.69</v>
       </c>
       <c r="D28">
-        <v>2568.229</v>
+        <v>1956.453</v>
       </c>
       <c r="E28">
-        <v>2902.838</v>
+        <v>2176.834</v>
       </c>
       <c r="F28">
-        <v>1756.715</v>
+        <v>8711.643</v>
       </c>
       <c r="G28">
-        <v>1640.464</v>
+        <v>8211.852000000001</v>
       </c>
       <c r="H28">
-        <v>1875.356</v>
+        <v>9219.311</v>
       </c>
       <c r="I28">
-        <v>205591412.935</v>
+        <v>80969976.535</v>
       </c>
       <c r="J28">
-        <v>193138989.874</v>
+        <v>76691738.742</v>
       </c>
       <c r="K28">
-        <v>218294943.42</v>
+        <v>85345794.93700001</v>
       </c>
       <c r="L28">
-        <v>233600083.842</v>
+        <v>1158686054.086</v>
       </c>
       <c r="M28">
-        <v>218069306.666</v>
+        <v>1092478563.49</v>
       </c>
       <c r="N28">
-        <v>249420658.776</v>
+        <v>1226101982.291</v>
       </c>
     </row>
     <row r="29">
@@ -1734,40 +1734,40 @@
         </is>
       </c>
       <c r="C29">
-        <v>126.422</v>
+        <v>106.822</v>
       </c>
       <c r="D29">
-        <v>115.161</v>
+        <v>98.931</v>
       </c>
       <c r="E29">
-        <v>138.179</v>
+        <v>114.898</v>
       </c>
       <c r="F29">
-        <v>13.66</v>
+        <v>4631.958</v>
       </c>
       <c r="G29">
-        <v>11.663</v>
+        <v>4258.176</v>
       </c>
       <c r="H29">
-        <v>15.807</v>
+        <v>5018.242</v>
       </c>
       <c r="I29">
-        <v>9506232.438999999</v>
+        <v>4186073.306</v>
       </c>
       <c r="J29">
-        <v>8667344.334000001</v>
+        <v>3879207.014</v>
       </c>
       <c r="K29">
-        <v>10388700.399</v>
+        <v>4503553.385</v>
       </c>
       <c r="L29">
-        <v>1817055.217</v>
+        <v>616169409.38</v>
       </c>
       <c r="M29">
-        <v>1550818.051</v>
+        <v>566401312.62</v>
       </c>
       <c r="N29">
-        <v>2104404.498</v>
+        <v>667543827.033</v>
       </c>
     </row>
     <row r="30">
@@ -1878,40 +1878,40 @@
         </is>
       </c>
       <c r="C32">
-        <v>685.878</v>
+        <v>595.348</v>
       </c>
       <c r="D32">
-        <v>645.664</v>
+        <v>560.46</v>
       </c>
       <c r="E32">
-        <v>726.61</v>
+        <v>630.862</v>
       </c>
       <c r="F32">
-        <v>5502.186</v>
+        <v>432.84</v>
       </c>
       <c r="G32">
-        <v>5170.708</v>
+        <v>407.242</v>
       </c>
       <c r="H32">
-        <v>5837.987</v>
+        <v>458.888</v>
       </c>
       <c r="I32">
-        <v>11549408.832</v>
+        <v>9911476.211999999</v>
       </c>
       <c r="J32">
-        <v>10871613.747</v>
+        <v>9327503.192</v>
       </c>
       <c r="K32">
-        <v>12236684.256</v>
+        <v>10506800.516</v>
       </c>
       <c r="L32">
-        <v>731758377.8430001</v>
+        <v>57558342.305</v>
       </c>
       <c r="M32">
-        <v>687706137.446</v>
+        <v>54150724.334</v>
       </c>
       <c r="N32">
-        <v>776732292.918</v>
+        <v>61037014.754</v>
       </c>
     </row>
     <row r="33">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="C33">
-        <v>1255.175</v>
+        <v>1107.36</v>
       </c>
       <c r="D33">
-        <v>1192.876</v>
+        <v>1052.609</v>
       </c>
       <c r="E33">
-        <v>1318.36</v>
+        <v>1162.974</v>
       </c>
       <c r="F33">
-        <v>7412.736</v>
+        <v>1926.319</v>
       </c>
       <c r="G33">
-        <v>7037.172</v>
+        <v>1829.08</v>
       </c>
       <c r="H33">
-        <v>7794.636</v>
+        <v>2025.167</v>
       </c>
       <c r="I33">
-        <v>21136648.636</v>
+        <v>18436512.801</v>
       </c>
       <c r="J33">
-        <v>20085749.864</v>
+        <v>17527127.925</v>
       </c>
       <c r="K33">
-        <v>22195381.019</v>
+        <v>19361407.278</v>
       </c>
       <c r="L33">
-        <v>985958726.145</v>
+        <v>256175899.31</v>
       </c>
       <c r="M33">
-        <v>936051418.516</v>
+        <v>243278808.526</v>
       </c>
       <c r="N33">
-        <v>1036672479.633</v>
+        <v>269378705.89</v>
       </c>
     </row>
     <row r="34">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="C34">
-        <v>6819.58</v>
+        <v>5986.723</v>
       </c>
       <c r="D34">
-        <v>6512.267</v>
+        <v>5719.045</v>
       </c>
       <c r="E34">
-        <v>7128.336</v>
+        <v>6254.603</v>
       </c>
       <c r="F34">
-        <v>26618.414</v>
+        <v>6330.04</v>
       </c>
       <c r="G34">
-        <v>25358.583</v>
+        <v>6044.929</v>
       </c>
       <c r="H34">
-        <v>27882.657</v>
+        <v>6616.585</v>
       </c>
       <c r="I34">
-        <v>114843091.676</v>
+        <v>99652968.25300001</v>
       </c>
       <c r="J34">
-        <v>109660138.058</v>
+        <v>95206864.23100001</v>
       </c>
       <c r="K34">
-        <v>120064348.003</v>
+        <v>104117553.969</v>
       </c>
       <c r="L34">
-        <v>3540132170.937</v>
+        <v>841916748.277</v>
       </c>
       <c r="M34">
-        <v>3372298356.312</v>
+        <v>803869412.465</v>
       </c>
       <c r="N34">
-        <v>3709424249.948</v>
+        <v>880240871.835</v>
       </c>
     </row>
     <row r="35">
@@ -2022,40 +2022,40 @@
         </is>
       </c>
       <c r="C35">
-        <v>17611.344</v>
+        <v>15842.705</v>
       </c>
       <c r="D35">
-        <v>16729.15</v>
+        <v>15060.423</v>
       </c>
       <c r="E35">
-        <v>18499.753</v>
+        <v>16624.177</v>
       </c>
       <c r="F35">
-        <v>34612.491</v>
+        <v>17564.307</v>
       </c>
       <c r="G35">
-        <v>32673.861</v>
+        <v>16691.88</v>
       </c>
       <c r="H35">
-        <v>36559.749</v>
+        <v>18446.975</v>
       </c>
       <c r="I35">
-        <v>296613159.171</v>
+        <v>263766438.273</v>
       </c>
       <c r="J35">
-        <v>281736511.717</v>
+        <v>250769436.889</v>
       </c>
       <c r="K35">
-        <v>311550483.726</v>
+        <v>276857479.488</v>
       </c>
       <c r="L35">
-        <v>4604240072.138</v>
+        <v>2336045289.122</v>
       </c>
       <c r="M35">
-        <v>4345282684.393</v>
+        <v>2220150134.089</v>
       </c>
       <c r="N35">
-        <v>4861200316.424</v>
+        <v>2452877495.335</v>
       </c>
     </row>
     <row r="36">
@@ -2070,40 +2070,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>24687.122</v>
+        <v>24728.545</v>
       </c>
       <c r="D36">
-        <v>22895.249</v>
+        <v>23059.479</v>
       </c>
       <c r="E36">
-        <v>26499.973</v>
+        <v>26408.554</v>
       </c>
       <c r="F36">
-        <v>7647.949</v>
+        <v>28969.709</v>
       </c>
       <c r="G36">
-        <v>6714.014</v>
+        <v>27007.193</v>
       </c>
       <c r="H36">
-        <v>8588.148999999999</v>
+        <v>30968.535</v>
       </c>
       <c r="I36">
-        <v>415817885.446</v>
+        <v>411629633.294</v>
       </c>
       <c r="J36">
-        <v>385475752.123</v>
+        <v>383855855.309</v>
       </c>
       <c r="K36">
-        <v>446299830.818</v>
+        <v>439592939.127</v>
       </c>
       <c r="L36">
-        <v>1016912845.068</v>
+        <v>3853917043.426</v>
       </c>
       <c r="M36">
-        <v>892930179.418</v>
+        <v>3589886307.677</v>
       </c>
       <c r="N36">
-        <v>1142805798.196</v>
+        <v>4117263422.492</v>
       </c>
     </row>
     <row r="37">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>70724.276</v>
+        <v>61306.466</v>
       </c>
       <c r="D37">
-        <v>65689.397</v>
+        <v>57168.568</v>
       </c>
       <c r="E37">
-        <v>75887.41499999999</v>
+        <v>65475.705</v>
       </c>
       <c r="F37">
-        <v>39950.362</v>
+        <v>39617.414</v>
       </c>
       <c r="G37">
-        <v>36888.031</v>
+        <v>36858.904</v>
       </c>
       <c r="H37">
-        <v>43098.095</v>
+        <v>42421.391</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>5312680305.951</v>
+        <v>5269397123.989</v>
       </c>
       <c r="M37">
-        <v>4909407868.156</v>
+        <v>4902610773.968</v>
       </c>
       <c r="N37">
-        <v>5733688185.568</v>
+        <v>5640243745.589</v>
       </c>
     </row>
     <row r="38">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>80422.93799999999</v>
+        <v>68742.618</v>
       </c>
       <c r="D38">
-        <v>75381.71799999999</v>
+        <v>64662.393</v>
       </c>
       <c r="E38">
-        <v>85544.181</v>
+        <v>72843.784</v>
       </c>
       <c r="F38">
-        <v>37866.327</v>
+        <v>37035.065</v>
       </c>
       <c r="G38">
-        <v>35350.33</v>
+        <v>34777.816</v>
       </c>
       <c r="H38">
-        <v>40441.472</v>
+        <v>39297.619</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>5035482298.574</v>
+        <v>4926069169.082</v>
       </c>
       <c r="M38">
-        <v>4700969878.751</v>
+        <v>4624887750.173</v>
       </c>
       <c r="N38">
-        <v>5378299751.578</v>
+        <v>5227194000.735</v>
       </c>
     </row>
     <row r="39">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="C39">
-        <v>92174.24800000001</v>
+        <v>78306.692</v>
       </c>
       <c r="D39">
-        <v>86707.242</v>
+        <v>73898.258</v>
       </c>
       <c r="E39">
-        <v>97706.401</v>
+        <v>82718.592</v>
       </c>
       <c r="F39">
-        <v>35879.772</v>
+        <v>34614.992</v>
       </c>
       <c r="G39">
-        <v>33555.925</v>
+        <v>32554.068</v>
       </c>
       <c r="H39">
-        <v>38253.115</v>
+        <v>36692.342</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2241,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>4771537315.121</v>
+        <v>4604034375.619</v>
       </c>
       <c r="M39">
-        <v>4463897171.493</v>
+        <v>4330814865.199</v>
       </c>
       <c r="N39">
-        <v>5087596164.28</v>
+        <v>4878673015.988</v>
       </c>
     </row>
     <row r="40">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="C40">
-        <v>85864.12</v>
+        <v>72740.97100000001</v>
       </c>
       <c r="D40">
-        <v>81506.564</v>
+        <v>69244.276</v>
       </c>
       <c r="E40">
-        <v>90279.197</v>
+        <v>76241.516</v>
       </c>
       <c r="F40">
-        <v>25502.629</v>
+        <v>24631.955</v>
       </c>
       <c r="G40">
-        <v>24092.157</v>
+        <v>23384.08</v>
       </c>
       <c r="H40">
-        <v>26940.337</v>
+        <v>25892.923</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>3392092370.755</v>
+        <v>3275905943.094</v>
       </c>
       <c r="M40">
-        <v>3203322144.206</v>
+        <v>3110104424.655</v>
       </c>
       <c r="N40">
-        <v>3583197320.783</v>
+        <v>3442574159.513</v>
       </c>
     </row>
     <row r="41">
@@ -2310,22 +2310,22 @@
         </is>
       </c>
       <c r="C41">
-        <v>90639.17200000001</v>
+        <v>76943.14</v>
       </c>
       <c r="D41">
-        <v>86368.946</v>
+        <v>73543.30100000001</v>
       </c>
       <c r="E41">
-        <v>94927.213</v>
+        <v>80352.452</v>
       </c>
       <c r="F41">
-        <v>18380.476</v>
+        <v>17711.512</v>
       </c>
       <c r="G41">
-        <v>17407.909</v>
+        <v>16853.689</v>
       </c>
       <c r="H41">
-        <v>19373.698</v>
+        <v>18573.822</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>2444539844.873</v>
+        <v>2355785180.957</v>
       </c>
       <c r="M41">
-        <v>2314452972.936</v>
+        <v>2241499588.525</v>
       </c>
       <c r="N41">
-        <v>2575843830.597</v>
+        <v>2470630410.279</v>
       </c>
     </row>
     <row r="42">
@@ -2358,22 +2358,22 @@
         </is>
       </c>
       <c r="C42">
-        <v>60379.554</v>
+        <v>52159.905</v>
       </c>
       <c r="D42">
-        <v>57186.366</v>
+        <v>49587.338</v>
       </c>
       <c r="E42">
-        <v>63615.236</v>
+        <v>54748.605</v>
       </c>
       <c r="F42">
-        <v>6463.39</v>
+        <v>6378.97</v>
       </c>
       <c r="G42">
-        <v>6053.589</v>
+        <v>6013.164</v>
       </c>
       <c r="H42">
-        <v>6879.138</v>
+        <v>6744.61</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>859662914.285</v>
+        <v>848342186.3839999</v>
       </c>
       <c r="M42">
-        <v>805466614.773</v>
+        <v>799547217.681</v>
       </c>
       <c r="N42">
-        <v>914916865.752</v>
+        <v>897063437.5700001</v>
       </c>
     </row>
     <row r="43">
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="C43">
-        <v>31338.3</v>
+        <v>29665.514</v>
       </c>
       <c r="D43">
-        <v>28971.958</v>
+        <v>27666.208</v>
       </c>
       <c r="E43">
-        <v>33728.6</v>
+        <v>31680.906</v>
       </c>
       <c r="F43">
-        <v>615.276</v>
+        <v>645.683</v>
       </c>
       <c r="G43">
-        <v>536.67</v>
+        <v>573.312</v>
       </c>
       <c r="H43">
-        <v>696.524</v>
+        <v>718.614</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>81819375.76100001</v>
+        <v>85849691.87</v>
       </c>
       <c r="M43">
-        <v>71322092.167</v>
+        <v>76265526.59</v>
       </c>
       <c r="N43">
-        <v>92619484.685</v>
+        <v>95558941.036</v>
       </c>
     </row>
   </sheetData>
